--- a/data/trans_orig/IP16A112_2023R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A112_2023R-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>63854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39655</t>
+          <t>39441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66336</t>
+          <t>60254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113233</t>
+          <t>112818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58768</t>
+          <t>58626</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97419</t>
+          <t>97111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61117</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80369</t>
+          <t>80583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>129270</t>
+          <t>129685</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176167</t>
+          <t>182249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26010</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31237</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36741</t>
+          <t>37343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53185</t>
+          <t>53471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>26070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28509</t>
+          <t>28364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35476</t>
+          <t>35190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51920</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>44851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90425</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69163</t>
+          <t>67953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93943</t>
+          <t>92577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114202</t>
+          <t>118007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172312</t>
+          <t>172866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88927</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135855</t>
+          <t>134501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88766</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113546</t>
+          <t>114756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189749</t>
+          <t>189195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>247859</t>
+          <t>244054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
